--- a/erp-server/erp-server-wms/src/main/resources/excel/SoDeliveryNoticeExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/SoDeliveryNoticeExport.xlsx
@@ -94,7 +94,7 @@
     <t>{.invalidStatusName}</t>
   </si>
   <si>
-    <t>{.deliveryStatusDictName}</t>
+    <t>{.deliveryStatusName}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -1145,7 +1145,7 @@
     <col min="4" max="4" width="24.625" customWidth="1"/>
     <col min="5" max="5" width="13.25" customWidth="1"/>
     <col min="6" max="6" width="7.625" customWidth="1"/>
-    <col min="7" max="7" width="15.875" customWidth="1"/>
+    <col min="7" max="7" width="23.75" customWidth="1"/>
     <col min="9" max="9" width="24.625" customWidth="1"/>
     <col min="10" max="10" width="13.125" customWidth="1"/>
     <col min="11" max="11" width="12.75" customWidth="1"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/SoDeliveryNoticeExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/SoDeliveryNoticeExport.xlsx
@@ -25,7 +25,7 @@
     <t>客户</t>
   </si>
   <si>
-    <t>发货组织</t>
+    <t>库存组织</t>
   </si>
   <si>
     <t>单据状态</t>
@@ -85,7 +85,7 @@
     <t>{.customerName}</t>
   </si>
   <si>
-    <t>{.deliveryOrgName}</t>
+    <t>{.warehouseOrgName}</t>
   </si>
   <si>
     <t>{.approveStatusName}</t>
